--- a/artfynd/A 30513-2026 artfynd.xlsx
+++ b/artfynd/A 30513-2026 artfynd.xlsx
@@ -897,7 +897,7 @@
         <v>136042742</v>
       </c>
       <c r="B4" t="n">
-        <v>93392</v>
+        <v>93395</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>136042770</v>
       </c>
       <c r="B5" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>136042876</v>
       </c>
       <c r="B6" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1250,7 +1250,7 @@
         <v>136042877</v>
       </c>
       <c r="B7" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2420,7 +2420,7 @@
         <v>136042757</v>
       </c>
       <c r="B17" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2884,7 +2884,7 @@
         <v>136042763</v>
       </c>
       <c r="B21" t="n">
-        <v>106483</v>
+        <v>106486</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3005,7 +3005,7 @@
         <v>136042764</v>
       </c>
       <c r="B22" t="n">
-        <v>106483</v>
+        <v>106486</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 30513-2026 artfynd.xlsx
+++ b/artfynd/A 30513-2026 artfynd.xlsx
@@ -897,7 +897,7 @@
         <v>136042742</v>
       </c>
       <c r="B4" t="n">
-        <v>93395</v>
+        <v>93396</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>136042770</v>
       </c>
       <c r="B5" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>136042876</v>
       </c>
       <c r="B6" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1250,7 +1250,7 @@
         <v>136042877</v>
       </c>
       <c r="B7" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2420,7 +2420,7 @@
         <v>136042757</v>
       </c>
       <c r="B17" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2884,7 +2884,7 @@
         <v>136042763</v>
       </c>
       <c r="B21" t="n">
-        <v>106486</v>
+        <v>106487</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3005,7 +3005,7 @@
         <v>136042764</v>
       </c>
       <c r="B22" t="n">
-        <v>106486</v>
+        <v>106487</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
